--- a/StructureDefinition-openimis-policy-holder-organization.xlsx
+++ b/StructureDefinition-openimis-policy-holder-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$147</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5999" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5485" uniqueCount="621">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1792,318 +1792,6 @@
   </si>
   <si>
     <t>ExtendedContactDetail.address</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Municipality/Ward</t>
-  </si>
-  <si>
-    <t>Insuree's Municipality/Ward name as it is configured in openIMIS.</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.extension:municipality</t>
-  </si>
-  <si>
-    <t>municipality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://github.com/openimis/openimis_fhir_r5_ig/StructureDefinition/address-municipality}
-</t>
-  </si>
-  <si>
-    <t>Municipality (Address)</t>
-  </si>
-  <si>
-    <t>The location level between District and City/Village.</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.extension:location</t>
-  </si>
-  <si>
-    <t>location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://github.com/openimis/openimis_fhir_r5_ig/StructureDefinition/address-location-reference}
-</t>
-  </si>
-  <si>
-    <t>Location Reference (Address)</t>
-  </si>
-  <si>
-    <t>The reference to address' location for City/Village level.</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.use</t>
-  </si>
-  <si>
-    <t>home | work | temp | old | billing - purpose of this address</t>
-  </si>
-  <si>
-    <t>The purpose of this address.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an address is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows an appropriate address to be chosen from a list of many.</t>
-  </si>
-  <si>
-    <t>home</t>
-  </si>
-  <si>
-    <t>The use of an address (home / work / etc.).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-use|5.0.0</t>
-  </si>
-  <si>
-    <t>Address.use</t>
-  </si>
-  <si>
-    <t>XAD.7</t>
-  </si>
-  <si>
-    <t>./AddressPurpose</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.type</t>
-  </si>
-  <si>
-    <t>postal | physical | both</t>
-  </si>
-  <si>
-    <t>Distinguishes between physical addresses (those you can visit) and mailing addresses (e.g. PO Boxes and care-of addresses). Most addresses are both.</t>
-  </si>
-  <si>
-    <t>The definition of Address states that "address is intended to describe postal addresses, not physical locations". However, many applications track whether an address has a dual purpose of being a location that can be visited as well as being a valid delivery destination, and Postal addresses are often used as proxies for physical locations (also see the [Location](http://hl7.org/fhir/R5/location.html#) resource).</t>
-  </si>
-  <si>
-    <t>physical</t>
-  </si>
-  <si>
-    <t>both</t>
-  </si>
-  <si>
-    <t>The type of an address (physical / postal).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/address-type|5.0.0</t>
-  </si>
-  <si>
-    <t>Address.type</t>
-  </si>
-  <si>
-    <t>XAD.18</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.text</t>
-  </si>
-  <si>
-    <t>Text representation of the address</t>
-  </si>
-  <si>
-    <t>Specifies the entire address as it should be displayed e.g. on a postal label. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating an address SHALL ensure that  when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street, Erewhon 9132</t>
-  </si>
-  <si>
-    <t>Address.text</t>
-  </si>
-  <si>
-    <t>XAD.1 + XAD.2 + XAD.3 + XAD.4 + XAD.5 + XAD.6</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.line</t>
-  </si>
-  <si>
-    <t>Street name, number, direction &amp; P.O. Box etc.</t>
-  </si>
-  <si>
-    <t>This component contains the house number, apartment number, street name, street direction,  P.O. Box number, delivery hints, and similar address information.</t>
-  </si>
-  <si>
-    <t>137 Nowhere Street</t>
-  </si>
-  <si>
-    <t>Address.line</t>
-  </si>
-  <si>
-    <t>XAD.1 + XAD.2 (note: XAD.1 and XAD.2 have different meanings for a company address than for a person address)</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = AL]</t>
-  </si>
-  <si>
-    <t>./StreetAddress (newline delimitted)</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.city</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municpality
-</t>
-  </si>
-  <si>
-    <t>City/Village</t>
-  </si>
-  <si>
-    <t>Insuree's City/Village name as it is configured in openIMIS.</t>
-  </si>
-  <si>
-    <t>Erewhon</t>
-  </si>
-  <si>
-    <t>Address.city</t>
-  </si>
-  <si>
-    <t>XAD.3</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CTY]</t>
-  </si>
-  <si>
-    <t>./Jurisdiction</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.district</t>
-  </si>
-  <si>
-    <t xml:space="preserve">County
-</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>PolicyHolder's District name as it is configured in openIMIS.</t>
-  </si>
-  <si>
-    <t>District is sometimes known as county, but in some regions 'county' is used in place of city (municipality), so county name should be conveyed in city instead.</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>Address.district</t>
-  </si>
-  <si>
-    <t>XAD.9</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT | CPA]</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.state</t>
-  </si>
-  <si>
-    <t>Province
-Territory</t>
-  </si>
-  <si>
-    <t>State/Region</t>
-  </si>
-  <si>
-    <t>PolicyHolder's State/Region name as it is configured in openIMIS.</t>
-  </si>
-  <si>
-    <t>Address.state</t>
-  </si>
-  <si>
-    <t>XAD.4</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = STA]</t>
-  </si>
-  <si>
-    <t>./Region</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.postalCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zip
-</t>
-  </si>
-  <si>
-    <t>Postal code for area</t>
-  </si>
-  <si>
-    <t>A postal code designating a region defined by the postal service.</t>
-  </si>
-  <si>
-    <t>9132</t>
-  </si>
-  <si>
-    <t>Address.postalCode</t>
-  </si>
-  <si>
-    <t>XAD.5</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = ZIP]</t>
-  </si>
-  <si>
-    <t>./PostalIdentificationCode</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.country</t>
-  </si>
-  <si>
-    <t>Country (e.g. may be ISO 3166 2 or 3 letter code)</t>
-  </si>
-  <si>
-    <t>Country - a nation as commonly understood or generally accepted.</t>
-  </si>
-  <si>
-    <t>ISO 3166 2- or 3- letter codes MAY be used in place of a human readable country name.</t>
-  </si>
-  <si>
-    <t>Address.country</t>
-  </si>
-  <si>
-    <t>XAD.6</t>
-  </si>
-  <si>
-    <t>AD.part[parttype = CNT]</t>
-  </si>
-  <si>
-    <t>./Country</t>
-  </si>
-  <si>
-    <t>Organization.contact.address.period</t>
-  </si>
-  <si>
-    <t>Time period when address was/is in use</t>
-  </si>
-  <si>
-    <t>Time period when address was/is in use.</t>
-  </si>
-  <si>
-    <t>Allows addresses to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>&lt;valuePeriod xmlns="http://hl7.org/fhir"&gt;
-  &lt;start value="2010-03-23"/&gt;
-  &lt;end value="2010-07-01"/&gt;
-&lt;/valuePeriod&gt;</t>
-  </si>
-  <si>
-    <t>Address.period</t>
-  </si>
-  <si>
-    <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
     <t>Organization.contact.organization</t>
@@ -2583,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO161"/>
+  <dimension ref="A1:AO147"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="43.58203125" customWidth="true" bestFit="true"/>
@@ -2596,7 +2284,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="86.234375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="86.0703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2605,7 +2293,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="34.26953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
@@ -2622,7 +2310,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="92.07421875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="48.16015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="25.11328125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="187.0625" customWidth="true" bestFit="true"/>
@@ -11084,7 +10772,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>22</v>
@@ -12734,7 +12422,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>22</v>
@@ -13321,7 +13009,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>22</v>
@@ -13787,7 +13475,7 @@
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>22</v>
@@ -14025,7 +13713,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>22</v>
@@ -14142,7 +13830,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>22</v>
@@ -14259,7 +13947,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>22</v>
@@ -14374,7 +14062,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>22</v>
@@ -14489,7 +14177,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>22</v>
@@ -18338,10 +18026,10 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>22</v>
@@ -18464,19 +18152,21 @@
         <v>22</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>93</v>
+        <v>297</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>176</v>
+        <v>575</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>177</v>
+        <v>576</v>
       </c>
       <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
+      <c r="O136" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P136" t="s" s="2">
         <v>22</v>
       </c>
@@ -18524,7 +18214,7 @@
         <v>22</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>178</v>
+        <v>578</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -18533,10 +18223,10 @@
         <v>91</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>22</v>
+        <v>103</v>
       </c>
       <c r="AK136" t="s" s="2">
         <v>22</v>
@@ -18545,7 +18235,7 @@
         <v>22</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>22</v>
@@ -18556,10 +18246,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18567,10 +18257,10 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>576</v>
+        <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>22</v>
@@ -18579,18 +18269,20 @@
         <v>22</v>
       </c>
       <c r="J137" t="s" s="2">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>138</v>
+        <v>289</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>22</v>
@@ -18627,31 +18319,31 @@
         <v>22</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>185</v>
+        <v>583</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>22</v>
@@ -18671,44 +18363,44 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C138" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H138" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J138" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I138" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>22</v>
-      </c>
       <c r="K138" t="s" s="2">
-        <v>581</v>
+        <v>297</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>22</v>
       </c>
@@ -18756,58 +18448,56 @@
         <v>22</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>185</v>
+        <v>584</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>22</v>
+        <v>357</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>22</v>
+        <v>588</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO138" t="s" s="2">
-        <v>22</v>
+        <v>180</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>22</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>22</v>
@@ -18816,16 +18506,18 @@
         <v>22</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>22</v>
       </c>
@@ -18873,7 +18565,7 @@
         <v>22</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>185</v>
+        <v>589</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -18885,7 +18577,7 @@
         <v>22</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>22</v>
@@ -18894,7 +18586,7 @@
         <v>22</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>22</v>
@@ -18905,10 +18597,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18919,32 +18611,28 @@
         <v>80</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>111</v>
+        <v>595</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
         <v>22</v>
       </c>
@@ -18956,49 +18644,49 @@
         <v>22</v>
       </c>
       <c r="T140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF140" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="U140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>22</v>
@@ -19013,21 +18701,21 @@
         <v>598</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO140" t="s" s="2">
-        <v>599</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19047,20 +18735,18 @@
         <v>22</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>111</v>
+        <v>228</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>601</v>
+        <v>176</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>22</v>
@@ -19070,10 +18756,10 @@
         <v>22</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>604</v>
+        <v>22</v>
       </c>
       <c r="T141" t="s" s="2">
-        <v>605</v>
+        <v>22</v>
       </c>
       <c r="U141" t="s" s="2">
         <v>22</v>
@@ -19085,13 +18771,13 @@
         <v>22</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>115</v>
+        <v>22</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>606</v>
+        <v>22</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>607</v>
+        <v>22</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>22</v>
@@ -19109,7 +18795,7 @@
         <v>22</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>608</v>
+        <v>178</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19118,19 +18804,19 @@
         <v>91</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>609</v>
+        <v>22</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>440</v>
+        <v>180</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>22</v>
@@ -19141,21 +18827,21 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>22</v>
@@ -19164,23 +18850,21 @@
         <v>22</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>611</v>
+        <v>182</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>612</v>
+        <v>183</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>22</v>
       </c>
@@ -19192,7 +18876,7 @@
         <v>22</v>
       </c>
       <c r="T142" t="s" s="2">
-        <v>614</v>
+        <v>22</v>
       </c>
       <c r="U142" t="s" s="2">
         <v>22</v>
@@ -19228,28 +18912,28 @@
         <v>22</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>615</v>
+        <v>185</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>616</v>
+        <v>22</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="AN142" t="s" s="2">
         <v>22</v>
@@ -19260,42 +18944,46 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>22</v>
+        <v>602</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="J143" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>604</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>22</v>
       </c>
@@ -19307,7 +18995,7 @@
         <v>22</v>
       </c>
       <c r="T143" t="s" s="2">
-        <v>620</v>
+        <v>22</v>
       </c>
       <c r="U143" t="s" s="2">
         <v>22</v>
@@ -19343,7 +19031,7 @@
         <v>22</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -19355,62 +19043,64 @@
         <v>22</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>622</v>
+        <v>22</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>623</v>
+        <v>136</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO143" t="s" s="2">
-        <v>624</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>626</v>
+        <v>22</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>228</v>
+        <v>163</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>22</v>
       </c>
@@ -19422,7 +19112,7 @@
         <v>22</v>
       </c>
       <c r="T144" t="s" s="2">
-        <v>629</v>
+        <v>22</v>
       </c>
       <c r="U144" t="s" s="2">
         <v>22</v>
@@ -19458,13 +19148,13 @@
         <v>22</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>22</v>
@@ -19476,28 +19166,28 @@
         <v>22</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>631</v>
+        <v>22</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>632</v>
+        <v>180</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO144" t="s" s="2">
-        <v>633</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>635</v>
+        <v>22</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
@@ -19507,26 +19197,24 @@
         <v>91</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>636</v>
+        <v>611</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>22</v>
@@ -19539,7 +19227,7 @@
         <v>22</v>
       </c>
       <c r="T145" t="s" s="2">
-        <v>639</v>
+        <v>22</v>
       </c>
       <c r="U145" t="s" s="2">
         <v>22</v>
@@ -19551,10 +19239,10 @@
         <v>22</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>22</v>
+        <v>366</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>22</v>
+        <v>613</v>
       </c>
       <c r="Z145" t="s" s="2">
         <v>22</v>
@@ -19575,10 +19263,10 @@
         <v>22</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>91</v>
@@ -19593,10 +19281,10 @@
         <v>22</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>641</v>
+        <v>22</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>642</v>
+        <v>180</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>22</v>
@@ -19607,42 +19295,44 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>643</v>
+        <v>614</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>644</v>
+        <v>22</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>22</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>228</v>
+        <v>289</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>645</v>
+        <v>615</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>646</v>
+        <v>616</v>
       </c>
       <c r="N146" s="2"/>
-      <c r="O146" s="2"/>
+      <c r="O146" t="s" s="2">
+        <v>617</v>
+      </c>
       <c r="P146" t="s" s="2">
         <v>22</v>
       </c>
@@ -19690,7 +19380,7 @@
         <v>22</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -19708,35 +19398,35 @@
         <v>22</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>648</v>
+        <v>22</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>649</v>
+        <v>180</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>650</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>651</v>
+        <v>618</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>652</v>
+        <v>22</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>22</v>
@@ -19745,16 +19435,16 @@
         <v>22</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>228</v>
+        <v>297</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>653</v>
+        <v>619</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>654</v>
+        <v>620</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -19769,7 +19459,7 @@
         <v>22</v>
       </c>
       <c r="T147" t="s" s="2">
-        <v>655</v>
+        <v>22</v>
       </c>
       <c r="U147" t="s" s="2">
         <v>22</v>
@@ -19805,7 +19495,7 @@
         <v>22</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>656</v>
+        <v>618</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
@@ -19823,1652 +19513,20 @@
         <v>22</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>657</v>
+        <v>22</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>658</v>
+        <v>180</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>22</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="148" hidden="true">
-      <c r="A148" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="B148" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="D148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E148" s="2"/>
-      <c r="F148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J148" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K148" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O148" s="2"/>
-      <c r="P148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q148" s="2"/>
-      <c r="R148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AG148" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH148" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ148" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL148" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="AM148" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AN148" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO148" t="s" s="2">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="150" hidden="true">
-      <c r="A150" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B150" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C150" s="2"/>
-      <c r="D150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E150" s="2"/>
-      <c r="F150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G150" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J150" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K150" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L150" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N150" s="2"/>
-      <c r="O150" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q150" s="2"/>
-      <c r="R150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF150" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ150" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AN150" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO150" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="151" hidden="true">
-      <c r="A151" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="B151" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="C151" s="2"/>
-      <c r="D151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E151" s="2"/>
-      <c r="F151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G151" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J151" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K151" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L151" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="O151" s="2"/>
-      <c r="P151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q151" s="2"/>
-      <c r="R151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AG151" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH151" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ151" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AN151" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO151" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="152" hidden="true">
-      <c r="A152" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="B152" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C152" s="2"/>
-      <c r="D152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E152" s="2"/>
-      <c r="F152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J152" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K152" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="P152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q152" s="2"/>
-      <c r="R152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ152" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="AN152" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO152" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="153" hidden="true">
-      <c r="A153" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="B153" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C153" s="2"/>
-      <c r="D153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E153" s="2"/>
-      <c r="F153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K153" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="L153" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="P153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q153" s="2"/>
-      <c r="R153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF153" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AG153" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH153" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ153" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO153" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="154" hidden="true">
-      <c r="A154" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="B154" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="C154" s="2"/>
-      <c r="D154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E154" s="2"/>
-      <c r="F154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K154" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="L154" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
-      <c r="P154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q154" s="2"/>
-      <c r="R154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF154" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="AG154" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH154" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ154" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL154" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AM154" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN154" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO154" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" hidden="true">
-      <c r="A155" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B155" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E155" s="2"/>
-      <c r="F155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K155" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
-      <c r="P155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q155" s="2"/>
-      <c r="R155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF155" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AG155" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH155" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI155" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AJ155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM155" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO155" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="156" hidden="true">
-      <c r="A156" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="E156" s="2"/>
-      <c r="F156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K156" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O156" s="2"/>
-      <c r="P156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q156" s="2"/>
-      <c r="R156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF156" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AG156" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH156" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ156" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM156" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN156" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO156" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="157" hidden="true">
-      <c r="A157" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B157" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="E157" s="2"/>
-      <c r="F157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I157" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J157" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K157" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L157" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M157" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="P157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q157" s="2"/>
-      <c r="R157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF157" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ157" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN157" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO157" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="158" hidden="true">
-      <c r="A158" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B158" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C158" s="2"/>
-      <c r="D158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E158" s="2"/>
-      <c r="F158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K158" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q158" s="2"/>
-      <c r="R158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM158" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN158" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO158" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="159" hidden="true">
-      <c r="A159" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C159" s="2"/>
-      <c r="D159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E159" s="2"/>
-      <c r="F159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K159" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="L159" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
-      <c r="P159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q159" s="2"/>
-      <c r="R159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X159" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="Y159" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="Z159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF159" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AG159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH159" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ159" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM159" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN159" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO159" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="160" hidden="true">
-      <c r="A160" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="C160" s="2"/>
-      <c r="D160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E160" s="2"/>
-      <c r="F160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K160" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="L160" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="P160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q160" s="2"/>
-      <c r="R160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF160" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AG160" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH160" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM160" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN160" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO160" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="161" hidden="true">
-      <c r="A161" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="C161" s="2"/>
-      <c r="D161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="E161" s="2"/>
-      <c r="F161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="I161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K161" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="M161" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="N161" s="2"/>
-      <c r="O161" s="2"/>
-      <c r="P161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Q161" s="2"/>
-      <c r="R161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="S161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AN161" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AO161" t="s" s="2">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO161">
+  <autoFilter ref="A1:AO147">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21478,7 +19536,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI160">
+  <conditionalFormatting sqref="A2:AI146">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-openimis-policy-holder-organization.xlsx
+++ b/StructureDefinition-openimis-policy-holder-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-policy-holder-organization.xlsx
+++ b/StructureDefinition-openimis-policy-holder-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
